--- a/TR_sem_outliers.xlsx
+++ b/TR_sem_outliers.xlsx
@@ -377,47 +377,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Bloco_4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bloco_5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Bloco_6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Bloco_7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bloco_8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Bloco_9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Bloco_10</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Bloco_11</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Bloco_3</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Bloco_4</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Bloco_5</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Bloco_6</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Bloco_7</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Bloco_8</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Bloco_9</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Bloco_10</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Bloco_11</t>
         </is>
       </c>
     </row>
@@ -431,28 +431,31 @@
         </is>
       </c>
       <c r="C2">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="D2">
-        <v>320</v>
+        <v>503.3333333333333</v>
       </c>
       <c r="E2">
-        <v>280</v>
-      </c>
-      <c r="F2">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="G2">
-        <v>240</v>
+        <v>476</v>
       </c>
       <c r="H2">
-        <v>270</v>
+        <v>476</v>
+      </c>
+      <c r="I2">
+        <v>440</v>
       </c>
       <c r="J2">
-        <v>302.5</v>
+        <v>498</v>
+      </c>
+      <c r="K2">
+        <v>535</v>
       </c>
       <c r="L2">
-        <v>250</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3">
@@ -471,31 +474,31 @@
         <v>396.6666666666667</v>
       </c>
       <c r="E3">
+        <v>431.6666666666667</v>
+      </c>
+      <c r="F3">
+        <v>416.6666666666667</v>
+      </c>
+      <c r="G3">
+        <v>396</v>
+      </c>
+      <c r="H3">
+        <v>352</v>
+      </c>
+      <c r="I3">
+        <v>364</v>
+      </c>
+      <c r="J3">
+        <v>370</v>
+      </c>
+      <c r="K3">
+        <v>388</v>
+      </c>
+      <c r="L3">
+        <v>340</v>
+      </c>
+      <c r="M3">
         <v>324</v>
-      </c>
-      <c r="F3">
-        <v>431.6666666666667</v>
-      </c>
-      <c r="G3">
-        <v>416.6666666666667</v>
-      </c>
-      <c r="H3">
-        <v>396</v>
-      </c>
-      <c r="I3">
-        <v>352</v>
-      </c>
-      <c r="J3">
-        <v>364</v>
-      </c>
-      <c r="K3">
-        <v>370</v>
-      </c>
-      <c r="L3">
-        <v>388</v>
-      </c>
-      <c r="M3">
-        <v>340</v>
       </c>
     </row>
     <row r="4">
@@ -508,34 +511,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>482</v>
+        <v>417.5</v>
       </c>
       <c r="D4">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="E4">
-        <v>396.6666666666667</v>
+        <v>386</v>
       </c>
       <c r="F4">
-        <v>456.6666666666667</v>
+        <v>370</v>
       </c>
       <c r="G4">
-        <v>402.5</v>
+        <v>390</v>
       </c>
       <c r="H4">
-        <v>355</v>
+        <v>408.3333333333333</v>
       </c>
       <c r="I4">
-        <v>426.6666666666667</v>
+        <v>338.3333333333333</v>
       </c>
       <c r="J4">
-        <v>340</v>
+        <v>386.6666666666667</v>
       </c>
       <c r="K4">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="L4">
-        <v>322.5</v>
+        <v>393.3333333333333</v>
+      </c>
+      <c r="M4">
+        <v>316</v>
       </c>
     </row>
     <row r="5">
@@ -548,34 +554,31 @@
         </is>
       </c>
       <c r="C5">
-        <v>330</v>
+        <v>525</v>
       </c>
       <c r="D5">
-        <v>313.3333333333333</v>
+        <v>470</v>
       </c>
       <c r="E5">
-        <v>310</v>
+        <v>446</v>
       </c>
       <c r="F5">
-        <v>295</v>
+        <v>515</v>
       </c>
       <c r="G5">
-        <v>322.5</v>
-      </c>
-      <c r="H5">
-        <v>320</v>
+        <v>468</v>
       </c>
       <c r="I5">
-        <v>300</v>
+        <v>460</v>
       </c>
       <c r="J5">
-        <v>370</v>
-      </c>
-      <c r="L5">
-        <v>375</v>
+        <v>480</v>
+      </c>
+      <c r="K5">
+        <v>426.6666666666667</v>
       </c>
       <c r="M5">
-        <v>356.6666666666667</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6">
@@ -594,31 +597,31 @@
         <v>281.6666666666667</v>
       </c>
       <c r="E6">
+        <v>265</v>
+      </c>
+      <c r="F6">
+        <v>271.6666666666667</v>
+      </c>
+      <c r="G6">
+        <v>278</v>
+      </c>
+      <c r="H6">
+        <v>290</v>
+      </c>
+      <c r="I6">
+        <v>285</v>
+      </c>
+      <c r="J6">
+        <v>311.6666666666667</v>
+      </c>
+      <c r="K6">
+        <v>313.3333333333333</v>
+      </c>
+      <c r="L6">
+        <v>276</v>
+      </c>
+      <c r="M6">
         <v>281.6666666666667</v>
-      </c>
-      <c r="F6">
-        <v>265</v>
-      </c>
-      <c r="G6">
-        <v>271.6666666666667</v>
-      </c>
-      <c r="H6">
-        <v>278</v>
-      </c>
-      <c r="I6">
-        <v>290</v>
-      </c>
-      <c r="J6">
-        <v>285</v>
-      </c>
-      <c r="K6">
-        <v>311.6666666666667</v>
-      </c>
-      <c r="L6">
-        <v>313.3333333333333</v>
-      </c>
-      <c r="M6">
-        <v>276</v>
       </c>
     </row>
     <row r="7">
@@ -637,31 +640,31 @@
         <v>452</v>
       </c>
       <c r="E7">
+        <v>282</v>
+      </c>
+      <c r="F7">
+        <v>428</v>
+      </c>
+      <c r="G7">
+        <v>386.6666666666667</v>
+      </c>
+      <c r="H7">
+        <v>380</v>
+      </c>
+      <c r="I7">
+        <v>296</v>
+      </c>
+      <c r="J7">
+        <v>435</v>
+      </c>
+      <c r="K7">
+        <v>380</v>
+      </c>
+      <c r="L7">
+        <v>365</v>
+      </c>
+      <c r="M7">
         <v>340</v>
-      </c>
-      <c r="F7">
-        <v>282</v>
-      </c>
-      <c r="G7">
-        <v>428</v>
-      </c>
-      <c r="H7">
-        <v>386.6666666666667</v>
-      </c>
-      <c r="I7">
-        <v>380</v>
-      </c>
-      <c r="J7">
-        <v>296</v>
-      </c>
-      <c r="K7">
-        <v>435</v>
-      </c>
-      <c r="L7">
-        <v>380</v>
-      </c>
-      <c r="M7">
-        <v>365</v>
       </c>
     </row>
     <row r="8">
@@ -674,34 +677,37 @@
         </is>
       </c>
       <c r="C8">
-        <v>442</v>
+        <v>270</v>
+      </c>
+      <c r="D8">
+        <v>365</v>
       </c>
       <c r="E8">
-        <v>350</v>
+        <v>283.3333333333333</v>
       </c>
       <c r="F8">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="G8">
-        <v>356.6666666666667</v>
+        <v>296.6666666666667</v>
       </c>
       <c r="H8">
-        <v>310</v>
+        <v>297.5</v>
       </c>
       <c r="I8">
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="J8">
-        <v>280</v>
+        <v>283.3333333333333</v>
       </c>
       <c r="K8">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L8">
-        <v>313.3333333333333</v>
+        <v>320</v>
       </c>
       <c r="M8">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -714,34 +720,37 @@
         </is>
       </c>
       <c r="C9">
-        <v>382.5</v>
+        <v>450</v>
       </c>
       <c r="D9">
         <v>370</v>
       </c>
+      <c r="E9">
+        <v>358.3333333333333</v>
+      </c>
       <c r="F9">
-        <v>276</v>
+        <v>426</v>
       </c>
       <c r="G9">
-        <v>267.5</v>
+        <v>408.3333333333333</v>
       </c>
       <c r="H9">
-        <v>308.3333333333333</v>
+        <v>368.3333333333333</v>
       </c>
       <c r="I9">
-        <v>296</v>
+        <v>406.6666666666667</v>
       </c>
       <c r="J9">
-        <v>285</v>
+        <v>403.3333333333333</v>
       </c>
       <c r="K9">
-        <v>320</v>
+        <v>416</v>
       </c>
       <c r="L9">
-        <v>314</v>
+        <v>416</v>
       </c>
       <c r="M9">
-        <v>360</v>
+        <v>363.3333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -760,31 +769,31 @@
         <v>301.6666666666667</v>
       </c>
       <c r="E10">
+        <v>240</v>
+      </c>
+      <c r="F10">
+        <v>276</v>
+      </c>
+      <c r="G10">
+        <v>278.3333333333333</v>
+      </c>
+      <c r="H10">
+        <v>258</v>
+      </c>
+      <c r="I10">
+        <v>266.6666666666667</v>
+      </c>
+      <c r="J10">
+        <v>268.3333333333333</v>
+      </c>
+      <c r="K10">
+        <v>266.6666666666667</v>
+      </c>
+      <c r="L10">
+        <v>270</v>
+      </c>
+      <c r="M10">
         <v>276.6666666666667</v>
-      </c>
-      <c r="F10">
-        <v>240</v>
-      </c>
-      <c r="G10">
-        <v>276</v>
-      </c>
-      <c r="H10">
-        <v>278.3333333333333</v>
-      </c>
-      <c r="I10">
-        <v>258</v>
-      </c>
-      <c r="J10">
-        <v>266.6666666666667</v>
-      </c>
-      <c r="K10">
-        <v>268.3333333333333</v>
-      </c>
-      <c r="L10">
-        <v>266.6666666666667</v>
-      </c>
-      <c r="M10">
-        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +812,31 @@
         <v>330</v>
       </c>
       <c r="E11">
+        <v>331.6666666666667</v>
+      </c>
+      <c r="F11">
+        <v>386.6666666666667</v>
+      </c>
+      <c r="G11">
+        <v>306.6666666666667</v>
+      </c>
+      <c r="H11">
+        <v>338.3333333333333</v>
+      </c>
+      <c r="I11">
+        <v>278.3333333333333</v>
+      </c>
+      <c r="J11">
+        <v>340</v>
+      </c>
+      <c r="K11">
+        <v>333.3333333333333</v>
+      </c>
+      <c r="L11">
+        <v>320</v>
+      </c>
+      <c r="M11">
         <v>378.3333333333333</v>
-      </c>
-      <c r="F11">
-        <v>331.6666666666667</v>
-      </c>
-      <c r="G11">
-        <v>386.6666666666667</v>
-      </c>
-      <c r="H11">
-        <v>306.6666666666667</v>
-      </c>
-      <c r="I11">
-        <v>338.3333333333333</v>
-      </c>
-      <c r="J11">
-        <v>278.3333333333333</v>
-      </c>
-      <c r="K11">
-        <v>340</v>
-      </c>
-      <c r="L11">
-        <v>333.3333333333333</v>
-      </c>
-      <c r="M11">
-        <v>320</v>
       </c>
     </row>
     <row r="12">
@@ -846,31 +855,31 @@
         <v>342</v>
       </c>
       <c r="E12">
+        <v>370</v>
+      </c>
+      <c r="F12">
+        <v>424</v>
+      </c>
+      <c r="G12">
+        <v>408.3333333333333</v>
+      </c>
+      <c r="H12">
+        <v>398.3333333333333</v>
+      </c>
+      <c r="I12">
+        <v>363.3333333333333</v>
+      </c>
+      <c r="J12">
+        <v>391.6666666666667</v>
+      </c>
+      <c r="K12">
+        <v>403.3333333333333</v>
+      </c>
+      <c r="L12">
+        <v>390</v>
+      </c>
+      <c r="M12">
         <v>385</v>
-      </c>
-      <c r="F12">
-        <v>370</v>
-      </c>
-      <c r="G12">
-        <v>424</v>
-      </c>
-      <c r="H12">
-        <v>408.3333333333333</v>
-      </c>
-      <c r="I12">
-        <v>398.3333333333333</v>
-      </c>
-      <c r="J12">
-        <v>363.3333333333333</v>
-      </c>
-      <c r="K12">
-        <v>391.6666666666667</v>
-      </c>
-      <c r="L12">
-        <v>403.3333333333333</v>
-      </c>
-      <c r="M12">
-        <v>390</v>
       </c>
     </row>
     <row r="13">
@@ -883,31 +892,37 @@
         </is>
       </c>
       <c r="C13">
-        <v>383.3333333333333</v>
+        <v>386</v>
+      </c>
+      <c r="D13">
+        <v>322.5</v>
       </c>
       <c r="E13">
-        <v>285</v>
+        <v>333.3333333333333</v>
+      </c>
+      <c r="F13">
+        <v>352</v>
       </c>
       <c r="G13">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="H13">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="I13">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="J13">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="K13">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="L13">
-        <v>250</v>
+        <v>386.6666666666667</v>
       </c>
       <c r="M13">
-        <v>310</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14">
@@ -926,31 +941,31 @@
         <v>320</v>
       </c>
       <c r="E14">
+        <v>346.6666666666667</v>
+      </c>
+      <c r="F14">
+        <v>320</v>
+      </c>
+      <c r="G14">
+        <v>361.6666666666667</v>
+      </c>
+      <c r="H14">
+        <v>353.3333333333333</v>
+      </c>
+      <c r="I14">
+        <v>358.3333333333333</v>
+      </c>
+      <c r="J14">
+        <v>395</v>
+      </c>
+      <c r="K14">
+        <v>420</v>
+      </c>
+      <c r="L14">
+        <v>403.3333333333333</v>
+      </c>
+      <c r="M14">
         <v>316</v>
-      </c>
-      <c r="F14">
-        <v>346.6666666666667</v>
-      </c>
-      <c r="G14">
-        <v>320</v>
-      </c>
-      <c r="H14">
-        <v>361.6666666666667</v>
-      </c>
-      <c r="I14">
-        <v>353.3333333333333</v>
-      </c>
-      <c r="J14">
-        <v>358.3333333333333</v>
-      </c>
-      <c r="K14">
-        <v>395</v>
-      </c>
-      <c r="L14">
-        <v>420</v>
-      </c>
-      <c r="M14">
-        <v>403.3333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -963,37 +978,31 @@
         </is>
       </c>
       <c r="C15">
-        <v>452</v>
+        <v>270</v>
       </c>
       <c r="D15">
-        <v>398.3333333333333</v>
+        <v>508</v>
       </c>
       <c r="E15">
-        <v>366.6666666666667</v>
+        <v>558.3333333333334</v>
       </c>
       <c r="F15">
-        <v>366.6666666666667</v>
+        <v>482</v>
       </c>
       <c r="G15">
-        <v>328</v>
-      </c>
-      <c r="H15">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="I15">
-        <v>372</v>
+        <v>530</v>
       </c>
       <c r="J15">
-        <v>406</v>
+        <v>504</v>
       </c>
       <c r="K15">
-        <v>411.6666666666667</v>
+        <v>557.5</v>
       </c>
       <c r="L15">
-        <v>398.3333333333333</v>
-      </c>
-      <c r="M15">
-        <v>443.3333333333333</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16">
@@ -1012,31 +1021,31 @@
         <v>380</v>
       </c>
       <c r="E16">
+        <v>376</v>
+      </c>
+      <c r="F16">
+        <v>302</v>
+      </c>
+      <c r="G16">
+        <v>427.5</v>
+      </c>
+      <c r="H16">
+        <v>328</v>
+      </c>
+      <c r="I16">
+        <v>353.3333333333333</v>
+      </c>
+      <c r="J16">
+        <v>334</v>
+      </c>
+      <c r="K16">
+        <v>350</v>
+      </c>
+      <c r="L16">
+        <v>338</v>
+      </c>
+      <c r="M16">
         <v>317.5</v>
-      </c>
-      <c r="F16">
-        <v>376</v>
-      </c>
-      <c r="G16">
-        <v>302</v>
-      </c>
-      <c r="H16">
-        <v>427.5</v>
-      </c>
-      <c r="I16">
-        <v>328</v>
-      </c>
-      <c r="J16">
-        <v>353.3333333333333</v>
-      </c>
-      <c r="K16">
-        <v>334</v>
-      </c>
-      <c r="L16">
-        <v>350</v>
-      </c>
-      <c r="M16">
-        <v>338</v>
       </c>
     </row>
     <row r="17">
@@ -1048,6 +1057,39 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C17">
+        <v>322.5</v>
+      </c>
+      <c r="D17">
+        <v>268</v>
+      </c>
+      <c r="E17">
+        <v>273.3333333333333</v>
+      </c>
+      <c r="F17">
+        <v>273.3333333333333</v>
+      </c>
+      <c r="G17">
+        <v>334</v>
+      </c>
+      <c r="H17">
+        <v>290</v>
+      </c>
+      <c r="I17">
+        <v>317.5</v>
+      </c>
+      <c r="J17">
+        <v>288.3333333333333</v>
+      </c>
+      <c r="K17">
+        <v>320</v>
+      </c>
+      <c r="L17">
+        <v>276</v>
+      </c>
+      <c r="M17">
+        <v>304</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1065,31 +1107,31 @@
         <v>308.3333333333333</v>
       </c>
       <c r="E18">
+        <v>345</v>
+      </c>
+      <c r="F18">
+        <v>365</v>
+      </c>
+      <c r="G18">
+        <v>273.3333333333333</v>
+      </c>
+      <c r="H18">
+        <v>250</v>
+      </c>
+      <c r="I18">
+        <v>285</v>
+      </c>
+      <c r="J18">
+        <v>275</v>
+      </c>
+      <c r="K18">
+        <v>288.3333333333333</v>
+      </c>
+      <c r="L18">
+        <v>312</v>
+      </c>
+      <c r="M18">
         <v>310</v>
-      </c>
-      <c r="F18">
-        <v>345</v>
-      </c>
-      <c r="G18">
-        <v>365</v>
-      </c>
-      <c r="H18">
-        <v>273.3333333333333</v>
-      </c>
-      <c r="I18">
-        <v>250</v>
-      </c>
-      <c r="J18">
-        <v>285</v>
-      </c>
-      <c r="K18">
-        <v>275</v>
-      </c>
-      <c r="L18">
-        <v>288.3333333333333</v>
-      </c>
-      <c r="M18">
-        <v>312</v>
       </c>
     </row>
     <row r="19">
@@ -1105,31 +1147,31 @@
         <v>445</v>
       </c>
       <c r="E19">
+        <v>460</v>
+      </c>
+      <c r="F19">
+        <v>391.6666666666667</v>
+      </c>
+      <c r="G19">
+        <v>422</v>
+      </c>
+      <c r="H19">
+        <v>360</v>
+      </c>
+      <c r="I19">
+        <v>400</v>
+      </c>
+      <c r="J19">
+        <v>508</v>
+      </c>
+      <c r="K19">
+        <v>430</v>
+      </c>
+      <c r="L19">
+        <v>462.5</v>
+      </c>
+      <c r="M19">
         <v>466.6666666666667</v>
-      </c>
-      <c r="F19">
-        <v>460</v>
-      </c>
-      <c r="G19">
-        <v>391.6666666666667</v>
-      </c>
-      <c r="H19">
-        <v>422</v>
-      </c>
-      <c r="I19">
-        <v>360</v>
-      </c>
-      <c r="J19">
-        <v>400</v>
-      </c>
-      <c r="K19">
-        <v>508</v>
-      </c>
-      <c r="L19">
-        <v>430</v>
-      </c>
-      <c r="M19">
-        <v>462.5</v>
       </c>
     </row>
     <row r="20">
@@ -1148,31 +1190,31 @@
         <v>382</v>
       </c>
       <c r="E20">
+        <v>328.3333333333333</v>
+      </c>
+      <c r="F20">
+        <v>354</v>
+      </c>
+      <c r="G20">
+        <v>296</v>
+      </c>
+      <c r="H20">
+        <v>332</v>
+      </c>
+      <c r="I20">
+        <v>336</v>
+      </c>
+      <c r="J20">
+        <v>353.3333333333333</v>
+      </c>
+      <c r="K20">
+        <v>340</v>
+      </c>
+      <c r="L20">
+        <v>351.6666666666667</v>
+      </c>
+      <c r="M20">
         <v>360</v>
-      </c>
-      <c r="F20">
-        <v>328.3333333333333</v>
-      </c>
-      <c r="G20">
-        <v>354</v>
-      </c>
-      <c r="H20">
-        <v>296</v>
-      </c>
-      <c r="I20">
-        <v>332</v>
-      </c>
-      <c r="J20">
-        <v>336</v>
-      </c>
-      <c r="K20">
-        <v>353.3333333333333</v>
-      </c>
-      <c r="L20">
-        <v>340</v>
-      </c>
-      <c r="M20">
-        <v>351.6666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -1191,31 +1233,31 @@
         <v>362</v>
       </c>
       <c r="E21">
+        <v>414</v>
+      </c>
+      <c r="F21">
+        <v>480</v>
+      </c>
+      <c r="G21">
+        <v>530</v>
+      </c>
+      <c r="H21">
+        <v>326.6666666666667</v>
+      </c>
+      <c r="I21">
+        <v>412.5</v>
+      </c>
+      <c r="J21">
+        <v>435</v>
+      </c>
+      <c r="K21">
+        <v>420</v>
+      </c>
+      <c r="L21">
+        <v>388</v>
+      </c>
+      <c r="M21">
         <v>378</v>
-      </c>
-      <c r="F21">
-        <v>414</v>
-      </c>
-      <c r="G21">
-        <v>480</v>
-      </c>
-      <c r="H21">
-        <v>530</v>
-      </c>
-      <c r="I21">
-        <v>326.6666666666667</v>
-      </c>
-      <c r="J21">
-        <v>412.5</v>
-      </c>
-      <c r="K21">
-        <v>435</v>
-      </c>
-      <c r="L21">
-        <v>420</v>
-      </c>
-      <c r="M21">
-        <v>388</v>
       </c>
     </row>
     <row r="22">
@@ -1234,31 +1276,31 @@
         <v>343.3333333333333</v>
       </c>
       <c r="E22">
+        <v>298</v>
+      </c>
+      <c r="F22">
+        <v>276.6666666666667</v>
+      </c>
+      <c r="G22">
+        <v>298</v>
+      </c>
+      <c r="H22">
+        <v>338.3333333333333</v>
+      </c>
+      <c r="I22">
+        <v>346.6666666666667</v>
+      </c>
+      <c r="J22">
+        <v>334</v>
+      </c>
+      <c r="K22">
+        <v>305</v>
+      </c>
+      <c r="L22">
+        <v>335</v>
+      </c>
+      <c r="M22">
         <v>303.3333333333333</v>
-      </c>
-      <c r="F22">
-        <v>298</v>
-      </c>
-      <c r="G22">
-        <v>276.6666666666667</v>
-      </c>
-      <c r="H22">
-        <v>298</v>
-      </c>
-      <c r="I22">
-        <v>338.3333333333333</v>
-      </c>
-      <c r="J22">
-        <v>346.6666666666667</v>
-      </c>
-      <c r="K22">
-        <v>334</v>
-      </c>
-      <c r="L22">
-        <v>305</v>
-      </c>
-      <c r="M22">
-        <v>335</v>
       </c>
     </row>
     <row r="23">
@@ -1277,31 +1319,31 @@
         <v>288.3333333333333</v>
       </c>
       <c r="E23">
+        <v>313.3333333333333</v>
+      </c>
+      <c r="F23">
+        <v>325</v>
+      </c>
+      <c r="G23">
+        <v>363.3333333333333</v>
+      </c>
+      <c r="H23">
+        <v>342</v>
+      </c>
+      <c r="I23">
+        <v>335</v>
+      </c>
+      <c r="J23">
+        <v>343.3333333333333</v>
+      </c>
+      <c r="K23">
+        <v>313.3333333333333</v>
+      </c>
+      <c r="L23">
+        <v>341.6666666666667</v>
+      </c>
+      <c r="M23">
         <v>300</v>
-      </c>
-      <c r="F23">
-        <v>313.3333333333333</v>
-      </c>
-      <c r="G23">
-        <v>325</v>
-      </c>
-      <c r="H23">
-        <v>363.3333333333333</v>
-      </c>
-      <c r="I23">
-        <v>342</v>
-      </c>
-      <c r="J23">
-        <v>335</v>
-      </c>
-      <c r="K23">
-        <v>343.3333333333333</v>
-      </c>
-      <c r="L23">
-        <v>313.3333333333333</v>
-      </c>
-      <c r="M23">
-        <v>341.6666666666667</v>
       </c>
     </row>
     <row r="24">
@@ -1320,31 +1362,31 @@
         <v>355</v>
       </c>
       <c r="E24">
+        <v>346.6666666666667</v>
+      </c>
+      <c r="F24">
+        <v>280</v>
+      </c>
+      <c r="G24">
+        <v>306.6666666666667</v>
+      </c>
+      <c r="H24">
+        <v>292</v>
+      </c>
+      <c r="I24">
+        <v>300</v>
+      </c>
+      <c r="J24">
+        <v>336.6666666666667</v>
+      </c>
+      <c r="K24">
+        <v>348</v>
+      </c>
+      <c r="L24">
+        <v>356.6666666666667</v>
+      </c>
+      <c r="M24">
         <v>387.5</v>
-      </c>
-      <c r="F24">
-        <v>346.6666666666667</v>
-      </c>
-      <c r="G24">
-        <v>280</v>
-      </c>
-      <c r="H24">
-        <v>306.6666666666667</v>
-      </c>
-      <c r="I24">
-        <v>292</v>
-      </c>
-      <c r="J24">
-        <v>300</v>
-      </c>
-      <c r="K24">
-        <v>336.6666666666667</v>
-      </c>
-      <c r="L24">
-        <v>348</v>
-      </c>
-      <c r="M24">
-        <v>356.6666666666667</v>
       </c>
     </row>
     <row r="25">
@@ -1363,31 +1405,31 @@
         <v>480</v>
       </c>
       <c r="E25">
+        <v>373.3333333333333</v>
+      </c>
+      <c r="F25">
+        <v>372</v>
+      </c>
+      <c r="G25">
+        <v>341.6666666666667</v>
+      </c>
+      <c r="H25">
+        <v>363.3333333333333</v>
+      </c>
+      <c r="I25">
+        <v>333.3333333333333</v>
+      </c>
+      <c r="J25">
+        <v>320</v>
+      </c>
+      <c r="K25">
+        <v>310</v>
+      </c>
+      <c r="L25">
+        <v>350</v>
+      </c>
+      <c r="M25">
         <v>343.3333333333333</v>
-      </c>
-      <c r="F25">
-        <v>373.3333333333333</v>
-      </c>
-      <c r="G25">
-        <v>372</v>
-      </c>
-      <c r="H25">
-        <v>341.6666666666667</v>
-      </c>
-      <c r="I25">
-        <v>363.3333333333333</v>
-      </c>
-      <c r="J25">
-        <v>333.3333333333333</v>
-      </c>
-      <c r="K25">
-        <v>320</v>
-      </c>
-      <c r="L25">
-        <v>310</v>
-      </c>
-      <c r="M25">
-        <v>350</v>
       </c>
     </row>
     <row r="26">
@@ -1406,31 +1448,31 @@
         <v>295</v>
       </c>
       <c r="E26">
+        <v>293.3333333333333</v>
+      </c>
+      <c r="F26">
+        <v>316.6666666666667</v>
+      </c>
+      <c r="G26">
+        <v>285</v>
+      </c>
+      <c r="H26">
+        <v>311.6666666666667</v>
+      </c>
+      <c r="I26">
+        <v>280</v>
+      </c>
+      <c r="J26">
+        <v>360</v>
+      </c>
+      <c r="K26">
+        <v>272</v>
+      </c>
+      <c r="L26">
+        <v>323.3333333333333</v>
+      </c>
+      <c r="M26">
         <v>286.6666666666667</v>
-      </c>
-      <c r="F26">
-        <v>293.3333333333333</v>
-      </c>
-      <c r="G26">
-        <v>316.6666666666667</v>
-      </c>
-      <c r="H26">
-        <v>285</v>
-      </c>
-      <c r="I26">
-        <v>311.6666666666667</v>
-      </c>
-      <c r="J26">
-        <v>280</v>
-      </c>
-      <c r="K26">
-        <v>360</v>
-      </c>
-      <c r="L26">
-        <v>272</v>
-      </c>
-      <c r="M26">
-        <v>323.3333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -1449,22 +1491,22 @@
         <v>444</v>
       </c>
       <c r="E27">
+        <v>434</v>
+      </c>
+      <c r="F27">
+        <v>517.5</v>
+      </c>
+      <c r="G27">
+        <v>462</v>
+      </c>
+      <c r="H27">
+        <v>415</v>
+      </c>
+      <c r="K27">
+        <v>467.5</v>
+      </c>
+      <c r="M27">
         <v>383.3333333333333</v>
-      </c>
-      <c r="F27">
-        <v>434</v>
-      </c>
-      <c r="G27">
-        <v>517.5</v>
-      </c>
-      <c r="H27">
-        <v>462</v>
-      </c>
-      <c r="I27">
-        <v>415</v>
-      </c>
-      <c r="L27">
-        <v>467.5</v>
       </c>
     </row>
     <row r="28">
@@ -1483,31 +1525,31 @@
         <v>346.6666666666667</v>
       </c>
       <c r="E28">
+        <v>395</v>
+      </c>
+      <c r="F28">
+        <v>290</v>
+      </c>
+      <c r="G28">
+        <v>348.3333333333333</v>
+      </c>
+      <c r="H28">
+        <v>390</v>
+      </c>
+      <c r="I28">
+        <v>290</v>
+      </c>
+      <c r="J28">
+        <v>418.3333333333333</v>
+      </c>
+      <c r="K28">
+        <v>446.6666666666667</v>
+      </c>
+      <c r="L28">
+        <v>372</v>
+      </c>
+      <c r="M28">
         <v>340</v>
-      </c>
-      <c r="F28">
-        <v>395</v>
-      </c>
-      <c r="G28">
-        <v>290</v>
-      </c>
-      <c r="H28">
-        <v>348.3333333333333</v>
-      </c>
-      <c r="I28">
-        <v>390</v>
-      </c>
-      <c r="J28">
-        <v>290</v>
-      </c>
-      <c r="K28">
-        <v>418.3333333333333</v>
-      </c>
-      <c r="L28">
-        <v>446.6666666666667</v>
-      </c>
-      <c r="M28">
-        <v>372</v>
       </c>
     </row>
     <row r="29">
@@ -1526,31 +1568,31 @@
         <v>450</v>
       </c>
       <c r="E29">
+        <v>425</v>
+      </c>
+      <c r="F29">
+        <v>392</v>
+      </c>
+      <c r="G29">
+        <v>404</v>
+      </c>
+      <c r="H29">
+        <v>396</v>
+      </c>
+      <c r="I29">
+        <v>334</v>
+      </c>
+      <c r="J29">
+        <v>423.3333333333333</v>
+      </c>
+      <c r="K29">
+        <v>395</v>
+      </c>
+      <c r="L29">
+        <v>438.3333333333333</v>
+      </c>
+      <c r="M29">
         <v>396.6666666666667</v>
-      </c>
-      <c r="F29">
-        <v>425</v>
-      </c>
-      <c r="G29">
-        <v>392</v>
-      </c>
-      <c r="H29">
-        <v>404</v>
-      </c>
-      <c r="I29">
-        <v>396</v>
-      </c>
-      <c r="J29">
-        <v>334</v>
-      </c>
-      <c r="K29">
-        <v>423.3333333333333</v>
-      </c>
-      <c r="L29">
-        <v>395</v>
-      </c>
-      <c r="M29">
-        <v>438.3333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -1569,31 +1611,31 @@
         <v>265</v>
       </c>
       <c r="E30">
-        <v>282</v>
+        <v>316.6666666666667</v>
       </c>
       <c r="F30">
-        <v>316.6666666666667</v>
+        <v>305</v>
       </c>
       <c r="G30">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="H30">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="I30">
         <v>310</v>
       </c>
       <c r="J30">
-        <v>310</v>
+        <v>336.6666666666667</v>
       </c>
       <c r="K30">
-        <v>336.6666666666667</v>
+        <v>338</v>
       </c>
       <c r="L30">
-        <v>338</v>
+        <v>313.3333333333333</v>
       </c>
       <c r="M30">
-        <v>313.3333333333333</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31">
@@ -1612,31 +1654,31 @@
         <v>335</v>
       </c>
       <c r="E31">
+        <v>396.6666666666667</v>
+      </c>
+      <c r="F31">
+        <v>327.5</v>
+      </c>
+      <c r="G31">
+        <v>378.3333333333333</v>
+      </c>
+      <c r="H31">
+        <v>386.6666666666667</v>
+      </c>
+      <c r="I31">
+        <v>376</v>
+      </c>
+      <c r="J31">
+        <v>388</v>
+      </c>
+      <c r="K31">
+        <v>370</v>
+      </c>
+      <c r="L31">
+        <v>376.6666666666667</v>
+      </c>
+      <c r="M31">
         <v>326.6666666666667</v>
-      </c>
-      <c r="F31">
-        <v>396.6666666666667</v>
-      </c>
-      <c r="G31">
-        <v>327.5</v>
-      </c>
-      <c r="H31">
-        <v>378.3333333333333</v>
-      </c>
-      <c r="I31">
-        <v>386.6666666666667</v>
-      </c>
-      <c r="J31">
-        <v>376</v>
-      </c>
-      <c r="K31">
-        <v>388</v>
-      </c>
-      <c r="L31">
-        <v>370</v>
-      </c>
-      <c r="M31">
-        <v>376.6666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -1655,31 +1697,31 @@
         <v>320</v>
       </c>
       <c r="E32">
+        <v>275</v>
+      </c>
+      <c r="F32">
+        <v>341.6666666666667</v>
+      </c>
+      <c r="G32">
+        <v>318.3333333333333</v>
+      </c>
+      <c r="H32">
+        <v>313.3333333333333</v>
+      </c>
+      <c r="I32">
+        <v>363.3333333333333</v>
+      </c>
+      <c r="J32">
+        <v>346</v>
+      </c>
+      <c r="K32">
+        <v>301.6666666666667</v>
+      </c>
+      <c r="L32">
+        <v>286</v>
+      </c>
+      <c r="M32">
         <v>286.6666666666667</v>
-      </c>
-      <c r="F32">
-        <v>275</v>
-      </c>
-      <c r="G32">
-        <v>341.6666666666667</v>
-      </c>
-      <c r="H32">
-        <v>318.3333333333333</v>
-      </c>
-      <c r="I32">
-        <v>313.3333333333333</v>
-      </c>
-      <c r="J32">
-        <v>363.3333333333333</v>
-      </c>
-      <c r="K32">
-        <v>346</v>
-      </c>
-      <c r="L32">
-        <v>301.6666666666667</v>
-      </c>
-      <c r="M32">
-        <v>286</v>
       </c>
     </row>
     <row r="33">
@@ -1698,31 +1740,31 @@
         <v>306.6666666666667</v>
       </c>
       <c r="E33">
+        <v>301.6666666666667</v>
+      </c>
+      <c r="F33">
+        <v>305</v>
+      </c>
+      <c r="G33">
+        <v>292</v>
+      </c>
+      <c r="H33">
+        <v>268</v>
+      </c>
+      <c r="I33">
         <v>316.6666666666667</v>
       </c>
-      <c r="F33">
-        <v>301.6666666666667</v>
-      </c>
-      <c r="G33">
-        <v>305</v>
-      </c>
-      <c r="H33">
-        <v>292</v>
-      </c>
-      <c r="I33">
-        <v>268</v>
-      </c>
       <c r="J33">
+        <v>310</v>
+      </c>
+      <c r="K33">
+        <v>323.3333333333333</v>
+      </c>
+      <c r="L33">
+        <v>358.3333333333333</v>
+      </c>
+      <c r="M33">
         <v>316.6666666666667</v>
-      </c>
-      <c r="K33">
-        <v>310</v>
-      </c>
-      <c r="L33">
-        <v>323.3333333333333</v>
-      </c>
-      <c r="M33">
-        <v>358.3333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -1741,31 +1783,31 @@
         <v>300</v>
       </c>
       <c r="E34">
+        <v>250</v>
+      </c>
+      <c r="F34">
+        <v>343.3333333333333</v>
+      </c>
+      <c r="G34">
+        <v>368.3333333333333</v>
+      </c>
+      <c r="H34">
+        <v>341.6666666666667</v>
+      </c>
+      <c r="I34">
+        <v>320</v>
+      </c>
+      <c r="J34">
+        <v>284</v>
+      </c>
+      <c r="K34">
+        <v>266</v>
+      </c>
+      <c r="L34">
+        <v>323.3333333333333</v>
+      </c>
+      <c r="M34">
         <v>295</v>
-      </c>
-      <c r="F34">
-        <v>250</v>
-      </c>
-      <c r="G34">
-        <v>343.3333333333333</v>
-      </c>
-      <c r="H34">
-        <v>368.3333333333333</v>
-      </c>
-      <c r="I34">
-        <v>341.6666666666667</v>
-      </c>
-      <c r="J34">
-        <v>320</v>
-      </c>
-      <c r="K34">
-        <v>284</v>
-      </c>
-      <c r="L34">
-        <v>266</v>
-      </c>
-      <c r="M34">
-        <v>323.3333333333333</v>
       </c>
     </row>
     <row r="35">
@@ -1784,28 +1826,28 @@
         <v>253.3333333333333</v>
       </c>
       <c r="E35">
+        <v>252</v>
+      </c>
+      <c r="F35">
+        <v>251.6666666666667</v>
+      </c>
+      <c r="G35">
+        <v>258.3333333333333</v>
+      </c>
+      <c r="H35">
+        <v>286</v>
+      </c>
+      <c r="I35">
+        <v>260</v>
+      </c>
+      <c r="K35">
+        <v>261.6666666666667</v>
+      </c>
+      <c r="L35">
+        <v>276.6666666666667</v>
+      </c>
+      <c r="M35">
         <v>265</v>
-      </c>
-      <c r="F35">
-        <v>252</v>
-      </c>
-      <c r="G35">
-        <v>251.6666666666667</v>
-      </c>
-      <c r="H35">
-        <v>258.3333333333333</v>
-      </c>
-      <c r="I35">
-        <v>286</v>
-      </c>
-      <c r="J35">
-        <v>260</v>
-      </c>
-      <c r="L35">
-        <v>261.6666666666667</v>
-      </c>
-      <c r="M35">
-        <v>276.6666666666667</v>
       </c>
     </row>
     <row r="36">
@@ -1824,31 +1866,31 @@
         <v>413.3333333333333</v>
       </c>
       <c r="E36">
+        <v>357.5</v>
+      </c>
+      <c r="F36">
+        <v>316.6666666666667</v>
+      </c>
+      <c r="G36">
+        <v>302.5</v>
+      </c>
+      <c r="H36">
+        <v>325</v>
+      </c>
+      <c r="I36">
+        <v>341.6666666666667</v>
+      </c>
+      <c r="J36">
+        <v>363.3333333333333</v>
+      </c>
+      <c r="K36">
+        <v>356.6666666666667</v>
+      </c>
+      <c r="L36">
+        <v>330</v>
+      </c>
+      <c r="M36">
         <v>378</v>
-      </c>
-      <c r="F36">
-        <v>357.5</v>
-      </c>
-      <c r="G36">
-        <v>316.6666666666667</v>
-      </c>
-      <c r="H36">
-        <v>302.5</v>
-      </c>
-      <c r="I36">
-        <v>325</v>
-      </c>
-      <c r="J36">
-        <v>341.6666666666667</v>
-      </c>
-      <c r="K36">
-        <v>363.3333333333333</v>
-      </c>
-      <c r="L36">
-        <v>356.6666666666667</v>
-      </c>
-      <c r="M36">
-        <v>330</v>
       </c>
     </row>
     <row r="37">
@@ -1867,31 +1909,31 @@
         <v>454</v>
       </c>
       <c r="E37">
+        <v>368.3333333333333</v>
+      </c>
+      <c r="F37">
+        <v>403.3333333333333</v>
+      </c>
+      <c r="G37">
+        <v>375</v>
+      </c>
+      <c r="H37">
+        <v>360</v>
+      </c>
+      <c r="I37">
+        <v>395</v>
+      </c>
+      <c r="J37">
+        <v>356.6666666666667</v>
+      </c>
+      <c r="K37">
+        <v>370</v>
+      </c>
+      <c r="L37">
+        <v>400</v>
+      </c>
+      <c r="M37">
         <v>383.3333333333333</v>
-      </c>
-      <c r="F37">
-        <v>368.3333333333333</v>
-      </c>
-      <c r="G37">
-        <v>403.3333333333333</v>
-      </c>
-      <c r="H37">
-        <v>375</v>
-      </c>
-      <c r="I37">
-        <v>360</v>
-      </c>
-      <c r="J37">
-        <v>395</v>
-      </c>
-      <c r="K37">
-        <v>356.6666666666667</v>
-      </c>
-      <c r="L37">
-        <v>370</v>
-      </c>
-      <c r="M37">
-        <v>400</v>
       </c>
     </row>
     <row r="38">
@@ -1910,31 +1952,31 @@
         <v>343.3333333333333</v>
       </c>
       <c r="E38">
+        <v>378.3333333333333</v>
+      </c>
+      <c r="F38">
+        <v>401.6666666666667</v>
+      </c>
+      <c r="G38">
+        <v>405</v>
+      </c>
+      <c r="H38">
+        <v>402</v>
+      </c>
+      <c r="I38">
+        <v>368.3333333333333</v>
+      </c>
+      <c r="J38">
+        <v>366.6666666666667</v>
+      </c>
+      <c r="K38">
+        <v>442.5</v>
+      </c>
+      <c r="L38">
+        <v>371.6666666666667</v>
+      </c>
+      <c r="M38">
         <v>386.6666666666667</v>
-      </c>
-      <c r="F38">
-        <v>378.3333333333333</v>
-      </c>
-      <c r="G38">
-        <v>401.6666666666667</v>
-      </c>
-      <c r="H38">
-        <v>405</v>
-      </c>
-      <c r="I38">
-        <v>402</v>
-      </c>
-      <c r="J38">
-        <v>368.3333333333333</v>
-      </c>
-      <c r="K38">
-        <v>366.6666666666667</v>
-      </c>
-      <c r="L38">
-        <v>442.5</v>
-      </c>
-      <c r="M38">
-        <v>371.6666666666667</v>
       </c>
     </row>
     <row r="39">
@@ -1952,14 +1994,14 @@
       <c r="D39">
         <v>506.6666666666667</v>
       </c>
-      <c r="E39">
+      <c r="H39">
+        <v>490</v>
+      </c>
+      <c r="K39">
+        <v>470</v>
+      </c>
+      <c r="M39">
         <v>502.5</v>
-      </c>
-      <c r="I39">
-        <v>490</v>
-      </c>
-      <c r="L39">
-        <v>470</v>
       </c>
     </row>
     <row r="40">
@@ -1972,37 +2014,37 @@
         </is>
       </c>
       <c r="C40">
-        <v>312.5</v>
+        <v>336.6666666666667</v>
       </c>
       <c r="D40">
-        <v>262</v>
+        <v>313.3333333333333</v>
       </c>
       <c r="E40">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="F40">
-        <v>286.6666666666667</v>
+        <v>351.6666666666667</v>
       </c>
       <c r="G40">
+        <v>346.6666666666667</v>
+      </c>
+      <c r="H40">
+        <v>346.6666666666667</v>
+      </c>
+      <c r="I40">
+        <v>353.3333333333333</v>
+      </c>
+      <c r="J40">
+        <v>331.6666666666667</v>
+      </c>
+      <c r="K40">
+        <v>310</v>
+      </c>
+      <c r="L40">
+        <v>376.6666666666667</v>
+      </c>
+      <c r="M40">
         <v>315</v>
-      </c>
-      <c r="H40">
-        <v>272</v>
-      </c>
-      <c r="I40">
-        <v>233.3333333333333</v>
-      </c>
-      <c r="J40">
-        <v>240</v>
-      </c>
-      <c r="K40">
-        <v>320</v>
-      </c>
-      <c r="L40">
-        <v>285</v>
-      </c>
-      <c r="M40">
-        <v>263.3333333333333</v>
       </c>
     </row>
     <row r="41">
@@ -2021,31 +2063,31 @@
         <v>412.5</v>
       </c>
       <c r="E41">
+        <v>322</v>
+      </c>
+      <c r="F41">
+        <v>394</v>
+      </c>
+      <c r="G41">
+        <v>368</v>
+      </c>
+      <c r="H41">
+        <v>358</v>
+      </c>
+      <c r="I41">
+        <v>351.6666666666667</v>
+      </c>
+      <c r="J41">
+        <v>356.6666666666667</v>
+      </c>
+      <c r="K41">
+        <v>378</v>
+      </c>
+      <c r="L41">
+        <v>384</v>
+      </c>
+      <c r="M41">
         <v>345</v>
-      </c>
-      <c r="F41">
-        <v>322</v>
-      </c>
-      <c r="G41">
-        <v>394</v>
-      </c>
-      <c r="H41">
-        <v>368</v>
-      </c>
-      <c r="I41">
-        <v>358</v>
-      </c>
-      <c r="J41">
-        <v>351.6666666666667</v>
-      </c>
-      <c r="K41">
-        <v>356.6666666666667</v>
-      </c>
-      <c r="L41">
-        <v>378</v>
-      </c>
-      <c r="M41">
-        <v>384</v>
       </c>
     </row>
   </sheetData>
